--- a/exports/trend_1d/INFY_full_report.xlsx
+++ b/exports/trend_1d/INFY_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42088</v>
+        <v>42089</v>
       </c>
       <c r="H2" t="n">
-        <v>543</v>
+        <v>525.2</v>
       </c>
       <c r="I2" t="n">
         <v>531.8689081931705</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K2" t="n">
-        <v>3.96</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>1.86</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>8.41</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42205</v>
+        <v>42206</v>
       </c>
       <c r="H3" t="n">
-        <v>490</v>
+        <v>544.5</v>
       </c>
       <c r="I3" t="n">
         <v>491.5593400406922</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K3" t="n">
-        <v>6.7</v>
+        <v>-3.67</v>
       </c>
       <c r="L3" t="n">
-        <v>5.94</v>
+        <v>7.06</v>
       </c>
       <c r="M3" t="n">
-        <v>1.47</v>
+        <v>3.37</v>
       </c>
       <c r="N3" t="n">
-        <v>2.87</v>
+        <v>11.12</v>
       </c>
       <c r="O3" t="n">
         <v>-3.28</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.7</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42241</v>
+        <v>42242</v>
       </c>
       <c r="H4" t="n">
-        <v>531.3</v>
+        <v>521</v>
       </c>
       <c r="I4" t="n">
         <v>522.9650136820558</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.42</v>
+        <v>-4.32</v>
       </c>
       <c r="L4" t="n">
         <v>6.98</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>13.5</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42277</v>
+        <v>42278</v>
       </c>
       <c r="H5" t="n">
-        <v>568.7</v>
+        <v>574.1</v>
       </c>
       <c r="I5" t="n">
         <v>574.0566409874184</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.16</v>
+        <v>-10.19</v>
       </c>
       <c r="L5" t="n">
-        <v>9.81</v>
+        <v>12.51</v>
       </c>
       <c r="M5" t="n">
         <v>2.66</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.08</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42324</v>
+        <v>42325</v>
       </c>
       <c r="H6" t="n">
-        <v>528.7</v>
+        <v>519.5</v>
       </c>
       <c r="I6" t="n">
         <v>527.6985240982017</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.91</v>
+        <v>-9.51</v>
       </c>
       <c r="L6" t="n">
-        <v>9.02</v>
+        <v>10.31</v>
       </c>
       <c r="M6" t="n">
         <v>1.62</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>7.66</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42382</v>
+        <v>42383</v>
       </c>
       <c r="H7" t="n">
-        <v>530.2</v>
+        <v>554.5</v>
       </c>
       <c r="I7" t="n">
         <v>542.0639964851028</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.06</v>
+        <v>-6.74</v>
       </c>
       <c r="L7" t="n">
-        <v>4.56</v>
+        <v>8.82</v>
       </c>
       <c r="M7" t="n">
         <v>1.04</v>
       </c>
       <c r="N7" t="n">
-        <v>3.17</v>
+        <v>4.58</v>
       </c>
       <c r="O7" t="n">
         <v>-1.74</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.9</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42410</v>
+        <v>42411</v>
       </c>
       <c r="H8" t="n">
-        <v>542.5</v>
+        <v>527.9</v>
       </c>
       <c r="I8" t="n">
         <v>538.0963576450434</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.16</v>
+        <v>-4.8</v>
       </c>
       <c r="L8" t="n">
         <v>6.94</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>9.74</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42431</v>
+        <v>42432</v>
       </c>
       <c r="H9" t="n">
-        <v>565.8</v>
+        <v>572.3</v>
       </c>
       <c r="I9" t="n">
         <v>572.1341598020844</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>-7.18</v>
+        <v>-8.41</v>
       </c>
       <c r="L9" t="n">
-        <v>7.86</v>
+        <v>10.59</v>
       </c>
       <c r="M9" t="n">
         <v>1.5</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.99</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42529</v>
+        <v>42530</v>
       </c>
       <c r="H10" t="n">
-        <v>605.9</v>
+        <v>580.2</v>
       </c>
       <c r="I10" t="n">
         <v>588.5355184445938</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K10" t="n">
-        <v>5.87</v>
+        <v>1.38</v>
       </c>
       <c r="L10" t="n">
         <v>3.46</v>
@@ -1011,7 +1130,7 @@
         <v>1.58</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>4.24</v>
       </c>
       <c r="O10" t="n">
         <v>1.15</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42460</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42712</v>
+        <v>42713</v>
       </c>
       <c r="H11" t="n">
-        <v>481.9</v>
+        <v>484.2</v>
       </c>
       <c r="I11" t="n">
         <v>482.1570773392468</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K11" t="n">
-        <v>16.94</v>
+        <v>16.55</v>
       </c>
       <c r="L11" t="n">
         <v>3.43</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>123</v>
+        <v>124</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>5.53</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42754</v>
+        <v>42755</v>
       </c>
       <c r="H12" t="n">
-        <v>468.9</v>
+        <v>464.3</v>
       </c>
       <c r="I12" t="n">
         <v>464.6970453079593</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.16</v>
+        <v>-4.11</v>
       </c>
       <c r="L12" t="n">
-        <v>4.17</v>
+        <v>4.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.77</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42779</v>
+        <v>42780</v>
       </c>
       <c r="H13" t="n">
-        <v>481.8</v>
+        <v>483.4</v>
       </c>
       <c r="I13" t="n">
         <v>482.9411817922262</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.77</v>
+        <v>-4.11</v>
       </c>
       <c r="L13" t="n">
-        <v>3.94</v>
+        <v>4.24</v>
       </c>
       <c r="M13" t="n">
         <v>0.46</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>7.28</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42832</v>
+        <v>42835</v>
       </c>
       <c r="H14" t="n">
-        <v>480.4</v>
+        <v>466.6</v>
       </c>
       <c r="I14" t="n">
         <v>478.8971635935324</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.62</v>
+        <v>-3.48</v>
       </c>
       <c r="L14" t="n">
-        <v>1.92</v>
+        <v>3.81</v>
       </c>
       <c r="M14" t="n">
         <v>1.32</v>
       </c>
       <c r="N14" t="n">
-        <v>2.32</v>
+        <v>2.87</v>
       </c>
       <c r="O14" t="n">
         <v>0.33</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.32</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42879</v>
+        <v>42880</v>
       </c>
       <c r="H15" t="n">
-        <v>467.3</v>
+        <v>481.2</v>
       </c>
       <c r="I15" t="n">
         <v>476.4555029312169</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.15</v>
+        <v>-3.13</v>
       </c>
       <c r="L15" t="n">
         <v>3.84</v>
@@ -1296,7 +1475,7 @@
         <v>0.93</v>
       </c>
       <c r="N15" t="n">
-        <v>2.12</v>
+        <v>2.97</v>
       </c>
       <c r="O15" t="n">
         <v>-2.87</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.34</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42902</v>
+        <v>42905</v>
       </c>
       <c r="H16" t="n">
-        <v>460.2</v>
+        <v>455.1</v>
       </c>
       <c r="I16" t="n">
         <v>458.4833263867866</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K16" t="n">
-        <v>-4.36</v>
+        <v>-5.42</v>
       </c>
       <c r="L16" t="n">
         <v>6.13</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.63</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42930</v>
+        <v>42933</v>
       </c>
       <c r="H17" t="n">
-        <v>475.7</v>
+        <v>481.6</v>
       </c>
       <c r="I17" t="n">
         <v>481.1905723175634</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.53</v>
+        <v>-5.82</v>
       </c>
       <c r="L17" t="n">
         <v>10.66</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>7.78</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42964</v>
+        <v>42965</v>
       </c>
       <c r="H18" t="n">
-        <v>499.6</v>
+        <v>451.9</v>
       </c>
       <c r="I18" t="n">
         <v>462.3309033379121</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" t="n">
-        <v>3.74</v>
+        <v>-6.17</v>
       </c>
       <c r="L18" t="n">
-        <v>2.95</v>
+        <v>10.15</v>
       </c>
       <c r="M18" t="n">
         <v>0.55</v>
       </c>
       <c r="N18" t="n">
-        <v>2.32</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="O18" t="n">
         <v>1.24</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42943</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>14.17</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43033</v>
+        <v>43034</v>
       </c>
       <c r="H19" t="n">
-        <v>457.7</v>
+        <v>463.6</v>
       </c>
       <c r="I19" t="n">
         <v>460.1710810183168</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.28</v>
+        <v>-2.59</v>
       </c>
       <c r="L19" t="n">
         <v>10.25</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.03</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43140</v>
+        <v>43143</v>
       </c>
       <c r="H20" t="n">
-        <v>542.8</v>
+        <v>539.7</v>
       </c>
       <c r="I20" t="n">
         <v>541.8362547487477</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K20" t="n">
-        <v>17.08</v>
+        <v>16.42</v>
       </c>
       <c r="L20" t="n">
         <v>3.19</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>8.470000000000001</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43210</v>
+        <v>43213</v>
       </c>
       <c r="H21" t="n">
-        <v>576.7</v>
+        <v>581.3</v>
       </c>
       <c r="I21" t="n">
         <v>579.0664239311637</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.86</v>
+        <v>-7.71</v>
       </c>
       <c r="L21" t="n">
-        <v>8.539999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="M21" t="n">
         <v>1.36</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>8.68</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43383</v>
+        <v>43384</v>
       </c>
       <c r="H22" t="n">
-        <v>685.6</v>
+        <v>659.1</v>
       </c>
       <c r="I22" t="n">
         <v>680.6882527572261</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K22" t="n">
-        <v>17.94</v>
+        <v>13.38</v>
       </c>
       <c r="L22" t="n">
         <v>3.58</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>7</v>
+      </c>
+      <c r="U22" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>10.58</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43437</v>
+        <v>43438</v>
       </c>
       <c r="H23" t="n">
-        <v>656.2</v>
+        <v>670.7</v>
       </c>
       <c r="I23" t="n">
         <v>660.3906135841499</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K23" t="n">
-        <v>0.44</v>
+        <v>-1.76</v>
       </c>
       <c r="L23" t="n">
         <v>7.19</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>9.07</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43454</v>
+        <v>43455</v>
       </c>
       <c r="H24" t="n">
-        <v>652.9</v>
+        <v>632.5</v>
       </c>
       <c r="I24" t="n">
         <v>634.830513637409</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.65</v>
+        <v>-5.7</v>
       </c>
       <c r="L24" t="n">
-        <v>4.2</v>
+        <v>6.1</v>
       </c>
       <c r="M24" t="n">
         <v>1.89</v>
       </c>
       <c r="N24" t="n">
-        <v>2.56</v>
+        <v>3.12</v>
       </c>
       <c r="O24" t="n">
         <v>2.21</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43476</v>
+        <v>43479</v>
       </c>
       <c r="H25" t="n">
-        <v>669</v>
+        <v>687</v>
       </c>
       <c r="I25" t="n">
         <v>679.5817537468195</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.77</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>6.75</v>
+        <v>9.91</v>
       </c>
       <c r="M25" t="n">
-        <v>2.41</v>
+        <v>3.44</v>
       </c>
       <c r="N25" t="n">
-        <v>1.98</v>
+        <v>2.69</v>
       </c>
       <c r="O25" t="n">
         <v>-3.12</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>6.74</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43531</v>
+        <v>43532</v>
       </c>
       <c r="H26" t="n">
-        <v>707.6</v>
+        <v>697.3</v>
       </c>
       <c r="I26" t="n">
         <v>705.5828270060822</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L26" t="n">
         <v>0.84</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>6.33</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43553</v>
+        <v>43556</v>
       </c>
       <c r="H27" t="n">
-        <v>728.1</v>
+        <v>739.1</v>
       </c>
       <c r="I27" t="n">
         <v>731.6359949329982</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.42</v>
+        <v>-5.99</v>
       </c>
       <c r="L27" t="n">
-        <v>4.99</v>
+        <v>6.68</v>
       </c>
       <c r="M27" t="n">
         <v>0.82</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>6.01</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43570</v>
+        <v>43571</v>
       </c>
       <c r="H28" t="n">
-        <v>712.1</v>
+        <v>708.8</v>
       </c>
       <c r="I28" t="n">
         <v>710.3407346766469</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.65</v>
+        <v>-4.1</v>
       </c>
       <c r="L28" t="n">
         <v>5.63</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>5.87</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43623</v>
+        <v>43626</v>
       </c>
       <c r="H29" t="n">
-        <v>723.4</v>
+        <v>737.5</v>
       </c>
       <c r="I29" t="n">
         <v>734.3033698745717</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.06</v>
+        <v>-4.05</v>
       </c>
       <c r="L29" t="n">
-        <v>4.09</v>
+        <v>4.13</v>
       </c>
       <c r="M29" t="n">
         <v>0.75</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>6.34</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43654</v>
+        <v>43655</v>
       </c>
       <c r="H30" t="n">
-        <v>702.4</v>
+        <v>700.3</v>
       </c>
       <c r="I30" t="n">
         <v>702.2399842740317</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.76</v>
+        <v>-5.04</v>
       </c>
       <c r="L30" t="n">
-        <v>5.46</v>
+        <v>5.9</v>
       </c>
       <c r="M30" t="n">
         <v>1.87</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>5.1</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43658</v>
+        <v>43661</v>
       </c>
       <c r="H31" t="n">
-        <v>711.4</v>
+        <v>762.8</v>
       </c>
       <c r="I31" t="n">
         <v>736.0454419024925</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.59</v>
+        <v>-8.92</v>
       </c>
       <c r="L31" t="n">
-        <v>2.11</v>
+        <v>9.25</v>
       </c>
       <c r="M31" t="n">
-        <v>0.3</v>
+        <v>4.98</v>
       </c>
       <c r="N31" t="n">
-        <v>0.74</v>
+        <v>7.23</v>
       </c>
       <c r="O31" t="n">
         <v>-0.3</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>8</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43728</v>
+        <v>43731</v>
       </c>
       <c r="H32" t="n">
-        <v>787.9</v>
+        <v>748.2</v>
       </c>
       <c r="I32" t="n">
         <v>778.9176032433178</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K32" t="n">
-        <v>3.29</v>
+        <v>-1.91</v>
       </c>
       <c r="L32" t="n">
-        <v>3.22</v>
+        <v>4.8</v>
       </c>
       <c r="M32" t="n">
         <v>1.45</v>
       </c>
       <c r="N32" t="n">
-        <v>3.17</v>
+        <v>5.04</v>
       </c>
       <c r="O32" t="n">
         <v>7.23</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.51</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43815</v>
+        <v>43816</v>
       </c>
       <c r="H33" t="n">
-        <v>698.9</v>
+        <v>714.2</v>
       </c>
       <c r="I33" t="n">
         <v>712.3446814038274</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K33" t="n">
-        <v>6.59</v>
+        <v>4.54</v>
       </c>
       <c r="L33" t="n">
         <v>7.78</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>6.53</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H34" t="n">
-        <v>761.4</v>
+        <v>716.2</v>
       </c>
       <c r="I34" t="n">
         <v>745.4025780692482</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K34" t="n">
-        <v>6.61</v>
+        <v>0.28</v>
       </c>
       <c r="L34" t="n">
         <v>2.93</v>
       </c>
       <c r="M34" t="n">
-        <v>1.09</v>
+        <v>3.59</v>
       </c>
       <c r="N34" t="n">
-        <v>1.96</v>
+        <v>5.94</v>
       </c>
       <c r="O34" t="n">
         <v>2.19</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43825</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,25 +2834,25 @@
         <v>8.4</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43916</v>
+        <v>43917</v>
       </c>
       <c r="H35" t="n">
-        <v>629.4</v>
+        <v>638.9</v>
       </c>
       <c r="I35" t="n">
         <v>638.661935565935</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K35" t="n">
-        <v>12.12</v>
+        <v>10.79</v>
       </c>
       <c r="L35" t="n">
         <v>5.72</v>
       </c>
       <c r="M35" t="n">
-        <v>2.36</v>
+        <v>3.43</v>
       </c>
       <c r="N35" t="n">
         <v>12.03</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>21.41</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44223</v>
+        <v>44224</v>
       </c>
       <c r="H36" t="n">
-        <v>1273.4</v>
+        <v>1249.2</v>
       </c>
       <c r="I36" t="n">
         <v>1252.312806194538</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K36" t="n">
-        <v>99.31</v>
+        <v>95.52</v>
       </c>
       <c r="L36" t="n">
         <v>10.82</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>209</v>
+        <v>210</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>10</v>
+      </c>
+      <c r="U36" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>8.49</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44264</v>
+        <v>44265</v>
       </c>
       <c r="H37" t="n">
-        <v>1317.1</v>
+        <v>1339.2</v>
       </c>
       <c r="I37" t="n">
         <v>1321.096187060186</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.44</v>
+        <v>-7.2</v>
       </c>
       <c r="L37" t="n">
-        <v>6.87</v>
+        <v>7.66</v>
       </c>
       <c r="M37" t="n">
         <v>1.52</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>7.36</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44308</v>
+        <v>44309</v>
       </c>
       <c r="H38" t="n">
-        <v>1322.5</v>
+        <v>1305.5</v>
       </c>
       <c r="I38" t="n">
         <v>1320.945415387352</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.25</v>
+        <v>-2.52</v>
       </c>
       <c r="L38" t="n">
         <v>3.99</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>8.52</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44341</v>
+        <v>44342</v>
       </c>
       <c r="H39" t="n">
-        <v>1332.8</v>
+        <v>1367.7</v>
       </c>
       <c r="I39" t="n">
         <v>1360.59127521081</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.09</v>
+        <v>-4.76</v>
       </c>
       <c r="L39" t="n">
-        <v>3.01</v>
+        <v>4.96</v>
       </c>
       <c r="M39" t="n">
         <v>0.88</v>
       </c>
       <c r="N39" t="n">
-        <v>1.5</v>
+        <v>2.62</v>
       </c>
       <c r="O39" t="n">
         <v>-1.29</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>6.03</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44468</v>
+        <v>44469</v>
       </c>
       <c r="H40" t="n">
-        <v>1656.4</v>
+        <v>1639.7</v>
       </c>
       <c r="I40" t="n">
         <v>1643.91982446514</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K40" t="n">
-        <v>21.11</v>
+        <v>19.89</v>
       </c>
       <c r="L40" t="n">
         <v>2.52</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>5</v>
+      </c>
+      <c r="U40" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>6.9</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44483</v>
+        <v>44487</v>
       </c>
       <c r="H41" t="n">
-        <v>1679.4</v>
+        <v>1754.2</v>
       </c>
       <c r="I41" t="n">
         <v>1731.80167985158</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.42</v>
+        <v>-6.98</v>
       </c>
       <c r="L41" t="n">
-        <v>6.47</v>
+        <v>7.39</v>
       </c>
       <c r="M41" t="n">
         <v>2.62</v>
       </c>
       <c r="N41" t="n">
-        <v>1.94</v>
+        <v>4.45</v>
       </c>
       <c r="O41" t="n">
         <v>-1.01</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>8.83</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44497</v>
+        <v>44498</v>
       </c>
       <c r="H42" t="n">
-        <v>1667.8</v>
+        <v>1632.4</v>
       </c>
       <c r="I42" t="n">
         <v>1645.343193818661</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.93</v>
+        <v>-6.94</v>
       </c>
       <c r="L42" t="n">
-        <v>5.85</v>
+        <v>7.31</v>
       </c>
       <c r="M42" t="n">
         <v>0.5600000000000001</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,28 +3386,28 @@
         <v>9.31</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44546</v>
+        <v>44547</v>
       </c>
       <c r="H43" t="n">
-        <v>1734.1</v>
+        <v>1782.3</v>
       </c>
       <c r="I43" t="n">
         <v>1763.248557086679</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K43" t="n">
-        <v>-6.23</v>
+        <v>-9.18</v>
       </c>
       <c r="L43" t="n">
-        <v>8.470000000000001</v>
+        <v>10.45</v>
       </c>
       <c r="M43" t="n">
-        <v>1.64</v>
+        <v>2.73</v>
       </c>
       <c r="N43" t="n">
-        <v>2.71</v>
+        <v>2.78</v>
       </c>
       <c r="O43" t="n">
         <v>-2.12</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>6.48</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44580</v>
+        <v>44581</v>
       </c>
       <c r="H44" t="n">
-        <v>1827.5</v>
+        <v>1785.1</v>
       </c>
       <c r="I44" t="n">
         <v>1793.239446061604</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K44" t="n">
-        <v>2.54</v>
+        <v>0.16</v>
       </c>
       <c r="L44" t="n">
         <v>1.85</v>
       </c>
       <c r="M44" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="N44" t="n">
         <v>2.87</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>7</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44629</v>
+        <v>44630</v>
       </c>
       <c r="H45" t="n">
-        <v>1774.9</v>
+        <v>1787.2</v>
       </c>
       <c r="I45" t="n">
         <v>1779.543773076017</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K45" t="n">
-        <v>0.57</v>
+        <v>-0.12</v>
       </c>
       <c r="L45" t="n">
         <v>1.33</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>7.75</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44659</v>
+        <v>44662</v>
       </c>
       <c r="H46" t="n">
-        <v>1776.2</v>
+        <v>1729.1</v>
       </c>
       <c r="I46" t="n">
         <v>1741.699527958177</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.62</v>
+        <v>-3.25</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>3.47</v>
       </c>
       <c r="M46" t="n">
         <v>1.05</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.67</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44749</v>
+        <v>44750</v>
       </c>
       <c r="H47" t="n">
-        <v>1467</v>
+        <v>1482.4</v>
       </c>
       <c r="I47" t="n">
         <v>1473.813468763622</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K47" t="n">
-        <v>15.16</v>
+        <v>14.27</v>
       </c>
       <c r="L47" t="n">
         <v>2.69</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>6.84</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44797</v>
+        <v>44798</v>
       </c>
       <c r="H48" t="n">
-        <v>1504.9</v>
+        <v>1486</v>
       </c>
       <c r="I48" t="n">
         <v>1491.052627578733</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K48" t="n">
-        <v>1.52</v>
+        <v>0.24</v>
       </c>
       <c r="L48" t="n">
         <v>6.85</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.79</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44848</v>
+        <v>44851</v>
       </c>
       <c r="H49" t="n">
-        <v>1443</v>
+        <v>1458.4</v>
       </c>
       <c r="I49" t="n">
         <v>1443.384251899292</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K49" t="n">
-        <v>2.89</v>
+        <v>1.86</v>
       </c>
       <c r="L49" t="n">
         <v>2.29</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.48</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44903</v>
+        <v>44904</v>
       </c>
       <c r="H50" t="n">
-        <v>1585.8</v>
+        <v>1536.1</v>
       </c>
       <c r="I50" t="n">
         <v>1538.013524088156</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K50" t="n">
-        <v>8.74</v>
+        <v>5.33</v>
       </c>
       <c r="L50" t="n">
         <v>1.06</v>
@@ -3291,7 +3890,7 @@
         <v>1.74</v>
       </c>
       <c r="N50" t="n">
-        <v>1.64</v>
+        <v>3.13</v>
       </c>
       <c r="O50" t="n">
         <v>1.07</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.86</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44943</v>
+        <v>44944</v>
       </c>
       <c r="H51" t="n">
-        <v>1506.9</v>
+        <v>1512.7</v>
       </c>
       <c r="I51" t="n">
         <v>1510.603747111174</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K51" t="n">
-        <v>1.9</v>
+        <v>1.52</v>
       </c>
       <c r="L51" t="n">
         <v>3.74</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>5.39</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44981</v>
+        <v>44984</v>
       </c>
       <c r="H52" t="n">
-        <v>1517.8</v>
+        <v>1477.3</v>
       </c>
       <c r="I52" t="n">
         <v>1488.349539505984</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K52" t="n">
-        <v>0.34</v>
+        <v>-2.34</v>
       </c>
       <c r="L52" t="n">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="M52" t="n">
         <v>1.04</v>
       </c>
       <c r="N52" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="O52" t="n">
         <v>0.38</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>6.44</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45071</v>
+        <v>45072</v>
       </c>
       <c r="H53" t="n">
-        <v>1276.7</v>
+        <v>1289.5</v>
       </c>
       <c r="I53" t="n">
         <v>1286.496939110172</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K53" t="n">
-        <v>13.58</v>
+        <v>12.71</v>
       </c>
       <c r="L53" t="n">
         <v>2.04</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>4.96</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45099</v>
+        <v>45100</v>
       </c>
       <c r="H54" t="n">
-        <v>1254.4</v>
+        <v>1238.2</v>
       </c>
       <c r="I54" t="n">
         <v>1238.722697260209</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.72</v>
+        <v>-3.98</v>
       </c>
       <c r="L54" t="n">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="M54" t="n">
         <v>1.22</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.74</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45105</v>
+        <v>45107</v>
       </c>
       <c r="H55" t="n">
-        <v>1266</v>
+        <v>1307.2</v>
       </c>
       <c r="I55" t="n">
         <v>1291.86380586353</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.25</v>
+        <v>-5.57</v>
       </c>
       <c r="L55" t="n">
-        <v>2.5</v>
+        <v>5.84</v>
       </c>
       <c r="M55" t="n">
-        <v>0.85</v>
+        <v>1.15</v>
       </c>
       <c r="N55" t="n">
-        <v>1.11</v>
+        <v>3.25</v>
       </c>
       <c r="O55" t="n">
         <v>-1.29</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>5.45</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45127</v>
+        <v>45128</v>
       </c>
       <c r="H56" t="n">
-        <v>1418.8</v>
+        <v>1303.4</v>
       </c>
       <c r="I56" t="n">
         <v>1355.218923678666</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K56" t="n">
-        <v>8.539999999999999</v>
+        <v>-0.29</v>
       </c>
       <c r="L56" t="n">
         <v>2.33</v>
       </c>
       <c r="M56" t="n">
-        <v>0.74</v>
+        <v>8.92</v>
       </c>
       <c r="N56" t="n">
-        <v>1.72</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="O56" t="n">
         <v>3.25</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>9.44</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45169</v>
+        <v>45170</v>
       </c>
       <c r="H57" t="n">
-        <v>1405</v>
+        <v>1413.3</v>
       </c>
       <c r="I57" t="n">
         <v>1412.855339674341</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K57" t="n">
-        <v>-7.79</v>
+        <v>-8.43</v>
       </c>
       <c r="L57" t="n">
-        <v>8.51</v>
+        <v>8.59</v>
       </c>
       <c r="M57" t="n">
         <v>1.24</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>4.2</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45196</v>
+        <v>45197</v>
       </c>
       <c r="H58" t="n">
-        <v>1435.9</v>
+        <v>1409</v>
       </c>
       <c r="I58" t="n">
         <v>1429.065513690851</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K58" t="n">
-        <v>1.6</v>
+        <v>-0.3</v>
       </c>
       <c r="L58" t="n">
         <v>1.09</v>
@@ -3747,7 +4442,7 @@
         <v>1.05</v>
       </c>
       <c r="N58" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="O58" t="n">
         <v>0.59</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>5.57</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45245</v>
+        <v>45246</v>
       </c>
       <c r="H59" t="n">
-        <v>1380.6</v>
+        <v>1414.3</v>
       </c>
       <c r="I59" t="n">
         <v>1402.256858165146</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K59" t="n">
-        <v>2.02</v>
+        <v>-0.38</v>
       </c>
       <c r="L59" t="n">
         <v>5.47</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.11</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45369</v>
+        <v>45370</v>
       </c>
       <c r="H60" t="n">
-        <v>1568.7</v>
+        <v>1528.4</v>
       </c>
       <c r="I60" t="n">
         <v>1566.532360332688</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K60" t="n">
-        <v>10.92</v>
+        <v>8.07</v>
       </c>
       <c r="L60" t="n">
         <v>2.38</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>5</v>
+      </c>
+      <c r="U60" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.48</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45448</v>
+        <v>45449</v>
       </c>
       <c r="H61" t="n">
-        <v>1399.8</v>
+        <v>1441.1</v>
       </c>
       <c r="I61" t="n">
         <v>1437.767073643579</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K61" t="n">
-        <v>8.41</v>
+        <v>5.71</v>
       </c>
       <c r="L61" t="n">
         <v>2.4</v>
@@ -3918,7 +4649,7 @@
         <v>2.35</v>
       </c>
       <c r="N61" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="O61" t="n">
         <v>-2.57</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>4</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>7.35</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H62" t="n">
-        <v>1782.6</v>
+        <v>1714.8</v>
       </c>
       <c r="I62" t="n">
         <v>1731.766722823073</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K62" t="n">
-        <v>23.7</v>
+        <v>18.99</v>
       </c>
       <c r="L62" t="n">
         <v>2.36</v>
       </c>
       <c r="M62" t="n">
-        <v>0.76</v>
+        <v>1.99</v>
       </c>
       <c r="N62" t="n">
-        <v>2.21</v>
+        <v>3.8</v>
       </c>
       <c r="O62" t="n">
         <v>2.95</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>3</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>7.5</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45530</v>
+        <v>45531</v>
       </c>
       <c r="H63" t="n">
-        <v>1836.4</v>
+        <v>1859.9</v>
       </c>
       <c r="I63" t="n">
         <v>1843.37630906198</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K63" t="n">
-        <v>-7.09</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>8.09</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="M63" t="n">
         <v>2.57</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.54</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45583</v>
+        <v>45586</v>
       </c>
       <c r="H64" t="n">
-        <v>1839.8</v>
+        <v>1813.5</v>
       </c>
       <c r="I64" t="n">
         <v>1823.827914642207</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.08</v>
+        <v>-2.49</v>
       </c>
       <c r="L64" t="n">
-        <v>1.73</v>
+        <v>3.27</v>
       </c>
       <c r="M64" t="n">
         <v>3.77</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>8.779999999999999</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45607</v>
+        <v>45608</v>
       </c>
       <c r="H65" t="n">
-        <v>1820.7</v>
+        <v>1829.2</v>
       </c>
       <c r="I65" t="n">
         <v>1824.426988343271</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.4</v>
+        <v>-0.87</v>
       </c>
       <c r="L65" t="n">
         <v>2.49</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>6.26</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45673</v>
+        <v>45674</v>
       </c>
       <c r="H66" t="n">
-        <v>1887.6</v>
+        <v>1777</v>
       </c>
       <c r="I66" t="n">
         <v>1832.603381217324</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K66" t="n">
-        <v>3.19</v>
+        <v>-2.85</v>
       </c>
       <c r="L66" t="n">
         <v>3.95</v>
       </c>
       <c r="M66" t="n">
-        <v>2.28</v>
+        <v>4.02</v>
       </c>
       <c r="N66" t="n">
-        <v>3.52</v>
+        <v>5.86</v>
       </c>
       <c r="O66" t="n">
         <v>0.47</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>9.25</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45786</v>
+        <v>45789</v>
       </c>
       <c r="H67" t="n">
-        <v>1475.7</v>
+        <v>1592.4</v>
       </c>
       <c r="I67" t="n">
         <v>1489.703924714008</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K67" t="n">
-        <v>16.96</v>
+        <v>10.39</v>
       </c>
       <c r="L67" t="n">
         <v>5.98</v>
@@ -4260,7 +5063,7 @@
         <v>2.57</v>
       </c>
       <c r="N67" t="n">
-        <v>3.66</v>
+        <v>7.91</v>
       </c>
       <c r="O67" t="n">
         <v>-5.86</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>5</v>
+      </c>
+      <c r="U67" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>10.25</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45862</v>
+        <v>45863</v>
       </c>
       <c r="H68" t="n">
-        <v>1519.6</v>
+        <v>1483.6</v>
       </c>
       <c r="I68" t="n">
         <v>1517.515765713636</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.57</v>
+        <v>-6.83</v>
       </c>
       <c r="L68" t="n">
-        <v>5.83</v>
+        <v>7.1</v>
       </c>
       <c r="M68" t="n">
         <v>2.27</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,25 +5180,25 @@
         <v>7.17</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45891</v>
+        <v>45894</v>
       </c>
       <c r="H69" t="n">
-        <v>1456</v>
+        <v>1499.6</v>
       </c>
       <c r="I69" t="n">
         <v>1473.389487314009</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K69" t="n">
-        <v>1.86</v>
+        <v>-1.08</v>
       </c>
       <c r="L69" t="n">
         <v>2.23</v>
       </c>
       <c r="M69" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="N69" t="n">
         <v>3.9</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>6.63</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45905</v>
+        <v>45908</v>
       </c>
       <c r="H70" t="n">
-        <v>1414</v>
+        <v>1402.6</v>
       </c>
       <c r="I70" t="n">
         <v>1408.894112049108</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K70" t="n">
-        <v>-5.71</v>
+        <v>-6.47</v>
       </c>
       <c r="L70" t="n">
-        <v>6.47</v>
+        <v>6.78</v>
       </c>
       <c r="M70" t="n">
         <v>0.59</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>7.08</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="H71" t="n">
-        <v>1490.2</v>
+        <v>1508</v>
       </c>
       <c r="I71" t="n">
         <v>1501.953625294793</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.25</v>
+        <v>-7.51</v>
       </c>
       <c r="L71" t="n">
-        <v>7.67</v>
+        <v>8.52</v>
       </c>
       <c r="M71" t="n">
         <v>3.35</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>5.33</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="H72" t="n">
-        <v>1453.4</v>
+        <v>1418.2</v>
       </c>
       <c r="I72" t="n">
         <v>1427.639632966465</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K72" t="n">
-        <v>-3.62</v>
+        <v>-5.95</v>
       </c>
       <c r="L72" t="n">
-        <v>4.16</v>
+        <v>6.45</v>
       </c>
       <c r="M72" t="n">
         <v>3.73</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>7.12</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="H73" t="n">
-        <v>1441.2</v>
+        <v>1496.1</v>
       </c>
       <c r="I73" t="n">
         <v>1489.026487851066</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.62</v>
+        <v>-5.49</v>
       </c>
       <c r="L73" t="n">
-        <v>5.03</v>
+        <v>6.71</v>
       </c>
       <c r="M73" t="n">
-        <v>1.17</v>
+        <v>2.55</v>
       </c>
       <c r="N73" t="n">
-        <v>2.5</v>
+        <v>3.81</v>
       </c>
       <c r="O73" t="n">
         <v>-2.42</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>6.43</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H74" t="n">
-        <v>1620.9</v>
+        <v>1503.3</v>
       </c>
       <c r="I74" t="n">
         <v>1553.035739621843</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K74" t="n">
-        <v>8.34</v>
+        <v>0.48</v>
       </c>
       <c r="L74" t="n">
         <v>5.19</v>
       </c>
       <c r="M74" t="n">
-        <v>1.41</v>
+        <v>4.95</v>
       </c>
       <c r="N74" t="n">
-        <v>2.52</v>
+        <v>7.26</v>
       </c>
       <c r="O74" t="n">
         <v>3.81</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>5</v>
+      </c>
+      <c r="U74" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>11.06</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="H75" t="n">
-        <v>1278.5</v>
+        <v>1311</v>
       </c>
       <c r="I75" t="n">
         <v>1307.831167149632</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K75" t="n">
-        <v>14.95</v>
+        <v>12.79</v>
       </c>
       <c r="L75" t="n">
         <v>3.19</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>10.22</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="H76" t="n">
-        <v>1214.3</v>
+        <v>1130.1</v>
       </c>
       <c r="I76" t="n">
         <v>1208.874165310254</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K76" t="n">
-        <v>-7.38</v>
+        <v>-13.8</v>
       </c>
       <c r="L76" t="n">
-        <v>8.470000000000001</v>
+        <v>13.97</v>
       </c>
       <c r="M76" t="n">
-        <v>1.58</v>
+        <v>3.27</v>
       </c>
       <c r="N76" t="n">
-        <v>3.4</v>
+        <v>6.93</v>
       </c>
       <c r="O76" t="n">
         <v>2.54</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,19 +5732,19 @@
         <v>13.74</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="H77" t="n">
-        <v>1136.3</v>
+        <v>1177</v>
       </c>
       <c r="I77" t="n">
         <v>1174.170151854924</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.55</v>
+        <v>-4.15</v>
       </c>
       <c r="L77" t="n">
         <v>6.01</v>
@@ -4839,7 +5762,19 @@
         <v>1</v>
       </c>
       <c r="Q77" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>3</v>
+      </c>
+      <c r="U77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>8.69</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="H78" t="n">
-        <v>1145.3</v>
+        <v>1114.6</v>
       </c>
       <c r="I78" t="n">
         <v>1120.938673522285</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K78" t="n">
-        <v>-2.69</v>
+        <v>-5.3</v>
       </c>
       <c r="L78" t="n">
-        <v>2.92</v>
+        <v>5.78</v>
       </c>
       <c r="M78" t="n">
         <v>2.26</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="H79" t="n">
-        <v>1068</v>
+        <v>1102.6</v>
       </c>
       <c r="I79" t="n">
         <v>1101.318665626202</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K79" t="n">
-        <v>4.18</v>
+        <v>1.08</v>
       </c>
       <c r="L79" t="n">
         <v>4.3</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>11.37</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="H80" t="n">
-        <v>1130</v>
+        <v>1087.5</v>
       </c>
       <c r="I80" t="n">
         <v>1099.417098201737</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K80" t="n">
-        <v>2.49</v>
+        <v>-1.37</v>
       </c>
       <c r="L80" t="n">
         <v>8.039999999999999</v>
@@ -5001,7 +5960,7 @@
         <v>3.13</v>
       </c>
       <c r="N80" t="n">
-        <v>2.51</v>
+        <v>3.76</v>
       </c>
       <c r="O80" t="n">
         <v>3.24</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H81" t="n">
-        <v>1062.1</v>
+        <v>1088</v>
       </c>
       <c r="I81" t="n">
         <v>1072.899736419895</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K81" t="n">
-        <v>2.34</v>
+        <v>-0.05</v>
       </c>
       <c r="L81" t="n">
         <v>2.06</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5118,6 +6101,14 @@
       <c r="Q82" t="n">
         <v>10</v>
       </c>
+      <c r="R82" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10076,7 +11067,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="6">
@@ -10086,7 +11077,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -10096,7 +11087,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="8">
@@ -10106,7 +11097,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
@@ -10116,7 +11107,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>65.5</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="10">
@@ -10126,7 +11117,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103.3</v>
+        <v>104.5</v>
       </c>
     </row>
     <row r="11">
@@ -10136,7 +11127,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -10146,7 +11137,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13">
@@ -10156,7 +11147,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>36.2</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="14">
@@ -10166,7 +11157,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.8</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="15">
@@ -10176,7 +11167,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.69</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="16">
@@ -10186,7 +11177,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.92</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="17">
@@ -10196,7 +11187,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>99.31</v>
+        <v>95.52</v>
       </c>
     </row>
     <row r="18">
@@ -10206,7 +11197,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.5</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="19">
@@ -10216,7 +11207,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.73</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="20">
@@ -10226,7 +11217,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.12</v>
+        <v>5.55</v>
       </c>
     </row>
     <row r="21">
@@ -10236,7 +11227,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.82</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="22">
@@ -10246,7 +11237,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -10256,7 +11247,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -10266,7 +11257,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="25">
@@ -10276,7 +11267,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.06</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="26">
@@ -10286,7 +11277,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.14</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="27">
@@ -10306,7 +11297,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
